--- a/artfynd/A 60157-2023 artfynd.xlsx
+++ b/artfynd/A 60157-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60157-2023 artfynd.xlsx
+++ b/artfynd/A 60157-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>82739933</v>
+        <v>62344058</v>
       </c>
       <c r="B2" t="n">
         <v>103427</v>
@@ -705,16 +705,23 @@
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Musåsen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574207.7385118544</v>
+        <v>574208.2058557173</v>
       </c>
       <c r="R2" t="n">
-        <v>6897279.810923297</v>
+        <v>6897279.821216097</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -739,14 +746,9 @@
           <t>Hassela</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>BES200408013011</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2004-08-01</t>
+          <t>2016-08-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -756,7 +758,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2004-08-01</t>
+          <t>2016-08-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -764,8 +766,13 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>f.d. äng NV om övergivet boningshus, ohävdat, förr slåtter, senblommande</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
@@ -775,150 +782,21 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Ödegård</t>
+          <t>f.d. ängsmark</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Björn Wannberg</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Stridh</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Hälsinglands flora (2019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>62344058</v>
-      </c>
-      <c r="B3" t="n">
-        <v>103427</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>221447</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Fältgentiana</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Musåsen, Hls</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>574208.2058557173</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6897279.821216097</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Nordanstig</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Hassela</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2016-08-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2016-08-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>f.d. äng NV om övergivet boningshus, ohävdat, förr slåtter, senblommande</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>f.d. ängsmark</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Tomas Troschke</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
           <t>Magnus Andersson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
